--- a/data/trans_dic/IP36A-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP36A-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adultos que perciben algun tipo de pensión</t>
+          <t>Adultos que perciben algun tipo de pensión (tasa de respuesta: 99,16%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,61; 28,74</t>
+          <t>11,75; 29,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,26; 24,99</t>
+          <t>9,72; 24,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,92; 23,22</t>
+          <t>7,3; 22,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,26; 55,13</t>
+          <t>15,48; 55,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,77; 30,44</t>
+          <t>12,05; 28,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,89; 24,45</t>
+          <t>9,53; 24,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,75; 33,65</t>
+          <t>13,52; 34,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,03; 48,94</t>
+          <t>22,03; 47,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,66; 25,34</t>
+          <t>14,1; 26,39</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,88; 22,06</t>
+          <t>11,91; 22,44</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,85; 25,05</t>
+          <t>12,81; 25,95</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22,66; 46,62</t>
+          <t>21,85; 45,97</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,32; 6,95</t>
+          <t>2,42; 7,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,9; 12,82</t>
+          <t>6,49; 12,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,58; 10,82</t>
+          <t>5,57; 10,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,8; 19,45</t>
+          <t>8,71; 19,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,69; 7,3</t>
+          <t>2,76; 7,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,39; 12,28</t>
+          <t>6,49; 11,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,68; 14,15</t>
+          <t>7,8; 14,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,03; 20,8</t>
+          <t>11,08; 20,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,07; 6,56</t>
+          <t>3,18; 6,42</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,44; 11,69</t>
+          <t>7,35; 11,58</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,54; 11,76</t>
+          <t>7,5; 11,67</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,36; 18,39</t>
+          <t>11,14; 18,44</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,45; 12,34</t>
+          <t>1,46; 13,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 12,48</t>
+          <t>1,26; 11,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 11,37</t>
+          <t>2,05; 11,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,19</t>
+          <t>0,0; 19,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,43</t>
+          <t>0,0; 12,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,36; 14,98</t>
+          <t>3,56; 15,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,58; 18,63</t>
+          <t>4,78; 18,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,71; 39,53</t>
+          <t>9,2; 40,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 9,8</t>
+          <t>1,82; 9,89</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,46; 11,59</t>
+          <t>3,5; 11,16</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,18; 12,98</t>
+          <t>4,21; 12,8</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,9; 24,09</t>
+          <t>6,64; 24,27</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,2; 10,21</t>
+          <t>5,15; 10,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,89; 12,72</t>
+          <t>7,73; 12,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,21; 11,0</t>
+          <t>6,17; 10,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,3; 21,24</t>
+          <t>10,27; 21,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,17; 9,66</t>
+          <t>4,95; 9,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,67; 12,52</t>
+          <t>7,65; 12,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,59; 15,5</t>
+          <t>9,4; 15,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,33; 23,07</t>
+          <t>14,81; 23,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,78; 9,02</t>
+          <t>5,68; 9,01</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,3; 11,86</t>
+          <t>8,28; 11,8</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,78; 12,64</t>
+          <t>8,7; 12,36</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,56; 20,82</t>
+          <t>13,57; 21,07</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que perciben algun tipo de pensión (tasa de respuesta: 99,16%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>11378</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10638</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6490</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>11316</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>10370</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>10202</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>11014</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>13026</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>21748</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>20841</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>17503</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>24342</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>6902; 17474</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6260; 15564</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3357; 10490</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5456; 19441</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>6347; 15234</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>6015; 15649</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>6555; 16579</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>8354; 17950</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>15711; 29395</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>15188; 28604</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>12095; 24512</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>15985; 33628</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>8538</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>24758</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>20416</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>28805</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>10354</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>25814</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>27842</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>29827</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>18892</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>50573</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>48258</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>58632</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>4738; 14100</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>16753; 33277</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>14156; 27924</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>17664; 39487</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>6135; 16515</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>18580; 34163</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>20162; 36680</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>21618; 40633</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>13302; 26815</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>39993; 63059</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>38427; 59770</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>44315; 73382</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2583</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3100</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2978</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1276</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>5101</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>5821</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>5198</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>3984</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>8201</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>8799</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>6474</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>689; 6389</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>777; 7102</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1169; 6800</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4299</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5169</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2249; 10065</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2734; 10788</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2293; 10005</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1600; 8707</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>4369; 13924</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>4808; 14635</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>3125; 11420</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>22499</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>38497</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>29884</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>41397</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>22125</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>41117</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>44676</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>48051</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>44624</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>79615</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>74560</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>89448</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>15541; 30403</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>29687; 48926</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>22052; 38235</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>26728; 56756</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>15633; 29705</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>31567; 51590</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>34212; 55659</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>38180; 61063</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>35070; 55613</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>65970; 93981</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>62753; 89150</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>70319; 109177</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP36A-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP36A-Estudios-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,75; 29,76</t>
+          <t>12,25; 28,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,72; 24,18</t>
+          <t>9,79; 24,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,3; 22,82</t>
+          <t>6,84; 23,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,48; 55,17</t>
+          <t>15,02; 53,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,05; 28,92</t>
+          <t>12,16; 28,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,53; 24,79</t>
+          <t>10,1; 25,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,52; 34,2</t>
+          <t>14,04; 35,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22,03; 47,34</t>
+          <t>22,15; 50,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,1; 26,39</t>
+          <t>14,28; 27,19</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,91; 22,44</t>
+          <t>11,6; 21,63</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12,81; 25,95</t>
+          <t>12,22; 25,73</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21,85; 45,97</t>
+          <t>22,84; 46,31</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,42; 7,21</t>
+          <t>2,43; 7,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,49; 12,89</t>
+          <t>6,63; 12,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,57; 10,99</t>
+          <t>5,76; 10,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,71; 19,46</t>
+          <t>8,74; 19,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,76; 7,44</t>
+          <t>2,9; 7,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,49; 11,94</t>
+          <t>6,47; 11,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,8; 14,2</t>
+          <t>8,1; 14,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,08; 20,83</t>
+          <t>10,74; 20,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,18; 6,42</t>
+          <t>3,19; 6,42</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,35; 11,58</t>
+          <t>7,45; 11,48</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,5; 11,67</t>
+          <t>7,51; 11,78</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,14; 18,44</t>
+          <t>11,19; 18,74</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,46; 13,57</t>
+          <t>1,25; 13,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 11,53</t>
+          <t>1,31; 12,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,05; 11,9</t>
+          <t>2,03; 12,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,43</t>
+          <t>0,0; 22,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,62</t>
+          <t>0,0; 11,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,56; 15,93</t>
+          <t>3,28; 15,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,78; 18,87</t>
+          <t>4,63; 19,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,2; 40,15</t>
+          <t>9,06; 37,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,82; 9,89</t>
+          <t>1,86; 9,45</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,5; 11,16</t>
+          <t>3,39; 11,35</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,21; 12,8</t>
+          <t>4,4; 12,69</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,64; 24,27</t>
+          <t>6,74; 23,38</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,15; 10,08</t>
+          <t>5,25; 10,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,73; 12,73</t>
+          <t>7,8; 12,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,17; 10,71</t>
+          <t>6,29; 10,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,27; 21,81</t>
+          <t>10,79; 21,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,95; 9,41</t>
+          <t>5,03; 9,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,65; 12,51</t>
+          <t>7,96; 12,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,4; 15,29</t>
+          <t>9,62; 15,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,81; 23,68</t>
+          <t>14,67; 23,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,68; 9,01</t>
+          <t>5,78; 9,05</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,28; 11,8</t>
+          <t>8,37; 11,81</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,7; 12,36</t>
+          <t>8,53; 12,41</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,57; 21,07</t>
+          <t>13,56; 20,74</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6902; 17474</t>
+          <t>7196; 16699</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6260; 15564</t>
+          <t>6299; 16057</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3357; 10490</t>
+          <t>3147; 10800</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5456; 19441</t>
+          <t>5293; 18709</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6347; 15234</t>
+          <t>6403; 15236</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6015; 15649</t>
+          <t>6376; 15933</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6555; 16579</t>
+          <t>6805; 17002</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8354; 17950</t>
+          <t>8398; 19018</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15711; 29395</t>
+          <t>15903; 30286</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15188; 28604</t>
+          <t>14791; 27583</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12095; 24512</t>
+          <t>11537; 24298</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15985; 33628</t>
+          <t>16709; 33877</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4738; 14100</t>
+          <t>4764; 14326</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16753; 33277</t>
+          <t>17133; 32988</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14156; 27924</t>
+          <t>14632; 27554</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17664; 39487</t>
+          <t>17729; 39747</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6135; 16515</t>
+          <t>6431; 16906</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18580; 34163</t>
+          <t>18502; 34214</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20162; 36680</t>
+          <t>20915; 37078</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21618; 40633</t>
+          <t>20954; 40264</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13302; 26815</t>
+          <t>13315; 26799</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39993; 63059</t>
+          <t>40550; 62506</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>38427; 59770</t>
+          <t>38470; 60360</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>44315; 73382</t>
+          <t>44545; 74597</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>689; 6389</t>
+          <t>586; 6318</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>777; 7102</t>
+          <t>806; 7594</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1169; 6800</t>
+          <t>1158; 6930</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4299</t>
+          <t>0; 4972</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5169</t>
+          <t>0; 4682</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2249; 10065</t>
+          <t>2075; 9502</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2734; 10788</t>
+          <t>2647; 10907</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2293; 10005</t>
+          <t>2256; 9374</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1600; 8707</t>
+          <t>1639; 8318</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4369; 13924</t>
+          <t>4230; 14160</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4808; 14635</t>
+          <t>5028; 14507</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3125; 11420</t>
+          <t>3172; 10997</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15541; 30403</t>
+          <t>15827; 30572</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29687; 48926</t>
+          <t>29964; 48322</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22052; 38235</t>
+          <t>22450; 38589</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26728; 56756</t>
+          <t>28086; 55108</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15633; 29705</t>
+          <t>15861; 30825</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31567; 51590</t>
+          <t>32842; 52389</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>34212; 55659</t>
+          <t>35004; 55841</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>38180; 61063</t>
+          <t>37838; 60364</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>35070; 55613</t>
+          <t>35680; 55861</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>65970; 93981</t>
+          <t>66666; 94083</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>62753; 89150</t>
+          <t>61533; 89457</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>70319; 109177</t>
+          <t>70261; 107481</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP36A-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP36A-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>19,69%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>16,16%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>22,72%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>33,79%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>19,37%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>16,53%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>14,12%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>32,11%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>19,69%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>16,16%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>22,72%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>32,73%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,25; 28,44</t>
+          <t>11,77; 30,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,79; 24,94</t>
+          <t>9,89; 24,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,84; 23,49</t>
+          <t>13,75; 33,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,02; 53,09</t>
+          <t>20,81; 48,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,16; 28,93</t>
+          <t>11,61; 28,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,1; 25,24</t>
+          <t>10,26; 24,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,04; 35,08</t>
+          <t>6,92; 23,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22,15; 50,16</t>
+          <t>17,19; 50,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,28; 27,19</t>
+          <t>13,66; 25,34</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,6; 21,63</t>
+          <t>11,88; 22,06</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12,22; 25,73</t>
+          <t>11,85; 25,05</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22,84; 46,31</t>
+          <t>23,28; 45,22</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4,66%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9,02%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>10,78%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>16,0%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>4,36%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>9,59%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>8,04%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>14,2%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,66%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>9,02%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>10,78%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>16,43%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,43; 7,32</t>
+          <t>2,69; 7,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,63; 12,77</t>
+          <t>6,39; 12,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,76; 10,85</t>
+          <t>7,68; 14,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,74; 19,59</t>
+          <t>11,57; 21,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,9; 7,62</t>
+          <t>2,32; 6,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,47; 11,96</t>
+          <t>6,9; 12,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,1; 14,35</t>
+          <t>5,58; 10,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,74; 20,64</t>
+          <t>12,43; 21,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,19; 6,42</t>
+          <t>3,07; 6,56</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,45; 11,48</t>
+          <t>7,44; 11,69</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,51; 11,78</t>
+          <t>7,54; 11,76</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,19; 18,74</t>
+          <t>13,29; 20,42</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3,42%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8,07%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>10,18%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>21,75%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>5,49%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>5,03%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>5,21%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,77%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3,42%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>8,07%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>10,18%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>14,15%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 13,42</t>
+          <t>0,0; 12,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 12,33</t>
+          <t>3,36; 14,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,03; 12,13</t>
+          <t>4,58; 18,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,47</t>
+          <t>9,4; 41,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,43</t>
+          <t>1,45; 12,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,28; 15,04</t>
+          <t>1,3; 12,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,63; 19,08</t>
+          <t>1,93; 11,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,06; 37,62</t>
+          <t>0,0; 19,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,86; 9,45</t>
+          <t>1,67; 9,8</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,39; 11,35</t>
+          <t>3,46; 11,59</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,4; 12,69</t>
+          <t>4,18; 12,98</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,74; 23,38</t>
+          <t>7,02; 24,68</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7,01%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9,97%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12,27%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>19,23%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>7,46%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>10,02%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>8,37%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>15,91%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,01%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,97%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12,27%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>18,47%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,25; 10,14</t>
+          <t>5,17; 9,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,8; 12,58</t>
+          <t>7,67; 12,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,29; 10,81</t>
+          <t>9,59; 15,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,79; 21,17</t>
+          <t>14,87; 23,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,03; 9,77</t>
+          <t>5,2; 10,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,96; 12,7</t>
+          <t>7,89; 12,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,62; 15,34</t>
+          <t>6,21; 11,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,67; 23,41</t>
+          <t>13,38; 22,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,78; 9,05</t>
+          <t>5,78; 9,02</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,37; 11,81</t>
+          <t>8,3; 11,86</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,53; 12,41</t>
+          <t>8,78; 12,64</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,56; 20,74</t>
+          <t>15,45; 21,98</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1373,37 +1373,37 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>10370</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10202</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11014</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>11983</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>11378</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>10638</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>6490</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>11316</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>10370</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>10202</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>11014</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13026</t>
+          <t>9058</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24342</t>
+          <t>21042</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7196; 16699</t>
+          <t>6199; 16035</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6299; 16057</t>
+          <t>6240; 15432</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3147; 10800</t>
+          <t>6666; 16312</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5293; 18709</t>
+          <t>7381; 17296</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6403; 15236</t>
+          <t>6818; 16880</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6376; 15933</t>
+          <t>6607; 16086</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6805; 17002</t>
+          <t>3181; 10677</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8398; 19018</t>
+          <t>4955; 14604</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15903; 30286</t>
+          <t>15213; 28233</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14791; 27583</t>
+          <t>15143; 28127</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11537; 24298</t>
+          <t>11189; 23662</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16709; 33877</t>
+          <t>14965; 29072</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>42</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>10354</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>25814</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>27842</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>28455</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>8538</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>24758</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>20416</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>28805</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>10354</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>25814</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>27842</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>29827</t>
+          <t>29491</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>58632</t>
+          <t>57947</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4764; 14326</t>
+          <t>5980; 16200</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17133; 32988</t>
+          <t>18284; 35149</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14632; 27554</t>
+          <t>19853; 36549</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17729; 39747</t>
+          <t>20579; 38878</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6431; 16906</t>
+          <t>4539; 13609</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18502; 34214</t>
+          <t>17819; 33102</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20915; 37078</t>
+          <t>14169; 27473</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20954; 40264</t>
+          <t>21739; 38098</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13315; 26799</t>
+          <t>12811; 27421</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>40550; 62506</t>
+          <t>40517; 63660</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>38470; 60360</t>
+          <t>38627; 60231</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>44545; 74597</t>
+          <t>46870; 72042</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5101</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5821</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4993</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>2583</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>3100</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>2978</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1276</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1400</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>5101</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>5821</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5198</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6474</t>
+          <t>6380</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>586; 6318</t>
+          <t>0; 5094</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>806; 7594</t>
+          <t>2124; 9466</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1158; 6930</t>
+          <t>2618; 10648</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4972</t>
+          <t>2159; 9514</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4682</t>
+          <t>685; 5806</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2075; 9502</t>
+          <t>799; 7689</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2647; 10907</t>
+          <t>1105; 6495</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2256; 9374</t>
+          <t>0; 4396</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1639; 8318</t>
+          <t>1474; 8630</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4230; 14160</t>
+          <t>4322; 14466</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5028; 14507</t>
+          <t>4784; 14842</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3172; 10997</t>
+          <t>3167; 11125</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>56</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>22125</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>41117</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>44676</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>45431</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>22499</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>38497</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>29884</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>41397</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>22125</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>41117</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>44676</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>48051</t>
+          <t>39937</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>89448</t>
+          <t>85368</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15827; 30572</t>
+          <t>16332; 30481</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29964; 48322</t>
+          <t>31626; 51651</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22450; 38589</t>
+          <t>34909; 56409</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28086; 55108</t>
+          <t>35136; 56314</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15861; 30825</t>
+          <t>15685; 30786</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>32842; 52389</t>
+          <t>30332; 48868</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35004; 55841</t>
+          <t>22178; 39283</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>37838; 60364</t>
+          <t>30227; 51476</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>35680; 55861</t>
+          <t>35697; 55657</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>66666; 94083</t>
+          <t>66123; 94443</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>61533; 89457</t>
+          <t>63317; 91117</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>70261; 107481</t>
+          <t>71378; 101591</t>
         </is>
       </c>
     </row>
